--- a/Luban/Config/Datas/Levels/L27/RoundData.xlsx
+++ b/Luban/Config/Datas/Levels/L27/RoundData.xlsx
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="F4" s="0" t="n">
-        <v>26</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="F5" s="0" t="n">
-        <v>26</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F6" s="0" t="n">
-        <v>26</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" customFormat="1" s="2">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="F7" s="0" t="n">
-        <v>26</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" customFormat="1" s="2">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="F8" s="0" t="n">
-        <v>39</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" customFormat="1" s="2">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="F9" s="0" t="n">
-        <v>28</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" customFormat="1" s="2">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="F10" s="0" t="n">
-        <v>28</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" customFormat="1" s="2">
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="F11" s="0" t="n">
-        <v>28</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" s="1">
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="F12" s="0" t="n">
-        <v>28</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" s="1">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="F13" s="0" t="n">
-        <v>42</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" s="1">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="F14" s="0" t="n">
-        <v>30</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" s="1">
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="F15" s="0" t="n">
-        <v>30</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" s="1">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="F16" s="0" t="n">
-        <v>30</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" s="1">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="F17" s="0" t="n">
-        <v>30</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" s="1">
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="F18" s="0" t="n">
-        <v>45</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" s="1">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="F19" s="0" t="n">
-        <v>32</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" s="1">
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="F20" s="0" t="n">
-        <v>32</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" s="1">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="F21" s="0" t="n">
-        <v>32</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22">
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="F22" s="0" t="n">
-        <v>32</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="F23" s="0" t="n">
-        <v>48</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24">
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="F24" s="0" t="n">
-        <v>34</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25">
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="F25" s="0" t="n">
-        <v>34</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="F26" s="0" t="n">
-        <v>34</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="F27" s="0" t="n">
-        <v>34</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28">
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F28" s="0" t="n">
-        <v>51</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/Levels/L27/RoundData.xlsx
+++ b/Luban/Config/Datas/Levels/L27/RoundData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="F4" s="0" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="F5" s="0" t="n">
-        <v>80</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F6" s="0" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" customFormat="1" s="2">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="F7" s="0" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" customFormat="1" s="2">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="F8" s="0" t="n">
-        <v>120</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" customFormat="1" s="2">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="F9" s="0" t="n">
-        <v>86</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" customFormat="1" s="2">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="F10" s="0" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" customFormat="1" s="2">
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="F11" s="0" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" s="1">
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="F12" s="0" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" s="1">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="F13" s="0" t="n">
-        <v>129</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" s="1">
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="F14" s="0" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" s="1">
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="F15" s="0" t="n">
-        <v>92</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" s="1">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="F16" s="0" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" s="1">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="F17" s="0" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" s="1">
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="F18" s="0" t="n">
-        <v>139</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" s="1">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="F19" s="0" t="n">
-        <v>99</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" s="1">
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="F20" s="0" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" s="1">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="F21" s="0" t="n">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22">
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="F22" s="0" t="n">
-        <v>99</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="F23" s="0" t="n">
-        <v>148</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24">
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="F24" s="0" t="n">
-        <v>105</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25">
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="F25" s="0" t="n">
-        <v>105</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="F26" s="0" t="n">
-        <v>105</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="F27" s="0" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28">
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F28" s="0" t="n">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
